--- a/testes/planilhas/rota-b.xlsx
+++ b/testes/planilhas/rota-b.xlsx
@@ -457,10 +457,10 @@
         <v>49000-201</v>
       </c>
       <c r="I2">
-        <v>-10.93</v>
+        <v>-10.9300013</v>
       </c>
       <c r="J2">
-        <v>-37.1</v>
+        <v>-37.1000013</v>
       </c>
     </row>
     <row r="3">
@@ -489,10 +489,10 @@
         <v>49000-202</v>
       </c>
       <c r="I3">
-        <v>-10.9313</v>
+        <v>-10.9313013</v>
       </c>
       <c r="J3">
-        <v>-37.1</v>
+        <v>-37.1000013</v>
       </c>
     </row>
     <row r="4">
@@ -521,10 +521,10 @@
         <v>49000-203</v>
       </c>
       <c r="I4">
-        <v>-10.93</v>
+        <v>-10.9300013</v>
       </c>
       <c r="J4">
-        <v>-37.09</v>
+        <v>-37.0900013</v>
       </c>
     </row>
     <row r="5">
@@ -553,10 +553,10 @@
         <v>49000-204</v>
       </c>
       <c r="I5">
-        <v>-10.93</v>
+        <v>-10.9300013</v>
       </c>
       <c r="J5">
-        <v>-37.08</v>
+        <v>-37.0800013</v>
       </c>
     </row>
     <row r="6">
@@ -585,10 +585,10 @@
         <v>49000-205</v>
       </c>
       <c r="I6">
-        <v>-10.93</v>
+        <v>-10.9300013</v>
       </c>
       <c r="J6">
-        <v>-37.07</v>
+        <v>-37.0700013</v>
       </c>
     </row>
     <row r="7">
@@ -617,10 +617,10 @@
         <v>49000-206</v>
       </c>
       <c r="I7">
-        <v>-10.93</v>
+        <v>-10.9300013</v>
       </c>
       <c r="J7">
-        <v>-37.06</v>
+        <v>-37.0600013</v>
       </c>
     </row>
   </sheetData>
